--- a/A3.xlsx
+++ b/A3.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kevin/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FD35066B-6D22-C442-9678-326052B8A63E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{FD03F5FA-6078-2641-83F0-FDD827622C26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="15720"/>
   </bookViews>
   <sheets>
-    <sheet name="936073_v1_dic_pacific_reefs" sheetId="1" r:id="rId1"/>
+    <sheet name="s1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
